--- a/nes-lter-mzb-info.xlsx
+++ b/nes-lter-mzb-info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmorkeski\Documents\nes-lter-microzooplankton-biomass-transect\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6193BA16-1177-41CA-B366-80984C3E73C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84B4FD5-183D-4355-BA36-1CFE728BBABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37650" yWindow="2205" windowWidth="27840" windowHeight="10320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ColumnHeadersBiomass" sheetId="6" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="136">
   <si>
     <t>attributeName</t>
   </si>
@@ -441,6 +441,15 @@
   </si>
   <si>
     <t>YYYY-MM-DDThh:mm:ssZ</t>
+  </si>
+  <si>
+    <t>micrometerPerPixel</t>
+  </si>
+  <si>
+    <t>micrometers per pixel at a given magnification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NES-LTER standard station. Where multiple depths were sampled, includes indicator of first or second depth sampled to correspond to the picture id. </t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1430,7 @@
         <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
@@ -1441,7 +1450,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
@@ -1461,7 +1470,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.6" customHeight="1">
@@ -1475,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.6" customHeight="1">
@@ -1489,7 +1498,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.6" customHeight="1">
@@ -1527,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -1568,6 +1577,23 @@
       </c>
       <c r="E2" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
